--- a/powerbi_report/Informatica_PySpark_Migration_Comparison.xlsx
+++ b/powerbi_report/Informatica_PySpark_Migration_Comparison.xlsx
@@ -483,12 +483,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>churndata, gender</t>
+          <t>Gender, Churndata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>churnratio, churndim, churndt</t>
+          <t>CHURNRATIO, CHURNDIM, ChurnDT</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -507,7 +507,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Multiple targets</t>
+          <t>Multiple targets (3), aggregation reduces rows</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>employee, ddept, emp_loc_empid</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tgt_flt, target_agg, ul_tgt_emp</t>
+          <t>TGT_FLT, TARGET_AGG, UL_TGT_EMP</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Multiple targets</t>
+          <t>Same source written to 3 targets</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employeedetails, dept, emp_loc</t>
+          <t>EMPLOYEEDETAILS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>target_emp</t>
+          <t>TARGET_EMP</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -591,12 +591,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>employee, ddept, emp_loc</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tgt_flt_mapplet</t>
+          <t>TGT_FLT</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1:1 mapping</t>
+          <t>1:1 mapping after filter</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>emp_dept, employee_details1, employee_details2, employeedetails, employee_details_flat</t>
+          <t>EMP_DEPT, EMPLOYEE_DETAILS1, EMPLOYEE_DETAILS2, EMPLOYEEDETAILS, EMPLOYEE_DETAILS_FLAT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>emp_max_min, t_emp_dep10, t_default, target_insert, target_update</t>
+          <t>EMP_MAX_MIN, T_EMP_DEP10, T_DEFAULT, TARGET_INSERT, TARGET_UPDATE</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Multiple targets</t>
+          <t>Union of 4 sources, router splits to 5 targets</t>
         </is>
       </c>
     </row>
@@ -666,309 +666,283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Job_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Table_Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Row_Count</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Column_Count</t>
+          <t>Table_Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Data_Type</t>
+          <t>Informatica_Row_Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Migration_Phase</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>churndata</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_m_PatternForChurnData</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Churndata</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>wf_m_PatternForChurnData</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_multiple_unc11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ddept</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_multiple_mapplet</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EMPLOYEEDETAILS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>emp_loc_empid</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_m_mapplet_multiple_unconnected</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employeedetails</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EMP_DEPT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EMPLOYEE_DETAILS1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>emp_loc</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EMPLOYEE_DETAILS2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>emp_dept</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EMPLOYEEDETAILS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>employee_details1</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EMPLOYEE_DETAILS_FLAT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>25</v>
       </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
-      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Before</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>employee_details2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>employee_details_flat</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>25</v>
-      </c>
-      <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Source (Informatica Input)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Before</t>
+          <t>Informatica</t>
         </is>
       </c>
     </row>
@@ -983,309 +957,358 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Job_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Table_Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Row_Count</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Column_Count</t>
+          <t>Table_Type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Data_Type</t>
+          <t>PySpark_Row_Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Migration_Phase</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>churnratio</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>wf_m_PatternForChurnData</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CHURNRATIO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>79</v>
       </c>
-      <c r="C2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>churndim</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_m_PatternForChurnData</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CHURNDIM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>churndt</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_m_PatternForChurnData</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ChurnDT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tgt_flt</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_multiple_unc11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TGT_FLT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>target_agg</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_multiple_unc11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TARGET_AGG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ul_tgt_emp</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>100</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_multiple_unc11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UL_TGT_EMP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>target_emp</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_multiple_mapplet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TARGET_EMP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>emp_max_min</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>175</v>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_m_mapplet_multiple_unconnected</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TGT_FLT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>t_emp_dep10</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>38</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EMP_MAX_MIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>175</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>t_default</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>137</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T_EMP_DEP10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>target_insert</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>49</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>137</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>After</t>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>target_update</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TARGET_INSERT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>49</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PySpark</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TARGET_UPDATE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
       </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Target (PySpark Output)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>After</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PySpark</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1361,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>churndata</t>
+          <t>Churndata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1363,7 +1386,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1388,7 +1411,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>churnratio</t>
+          <t>CHURNRATIO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1413,7 +1436,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>churndim</t>
+          <t>CHURNDIM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1438,7 +1461,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>churndt</t>
+          <t>ChurnDT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1463,7 +1486,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1488,7 +1511,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tgt_flt</t>
+          <t>TGT_FLT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1513,7 +1536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>target_agg</t>
+          <t>TARGET_AGG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1538,7 +1561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ul_tgt_emp</t>
+          <t>UL_TGT_EMP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1563,7 +1586,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employeedetails</t>
+          <t>EMPLOYEEDETAILS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1588,7 +1611,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>target_emp</t>
+          <t>TARGET_EMP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1613,7 +1636,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee</t>
+          <t>EMPLOYEE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1638,7 +1661,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tgt_flt</t>
+          <t>TGT_FLT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1663,7 +1686,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emp_dept</t>
+          <t>EMP_DEPT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1688,7 +1711,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employee_details1</t>
+          <t>EMPLOYEE_DETAILS1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1697,7 +1720,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1713,7 +1736,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>employee_details2</t>
+          <t>EMPLOYEE_DETAILS2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1722,7 +1745,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1738,7 +1761,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employeedetails</t>
+          <t>EMPLOYEEDETAILS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1763,7 +1786,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employee_details_flat</t>
+          <t>EMPLOYEE_DETAILS_FLAT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1788,7 +1811,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>emp_max_min</t>
+          <t>EMP_MAX_MIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1813,7 +1836,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t_emp_dep10</t>
+          <t>T_EMP_DEP10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1838,7 +1861,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t_default</t>
+          <t>T_DEFAULT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1863,7 +1886,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>target_insert</t>
+          <t>TARGET_INSERT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1888,7 +1911,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>target_update</t>
+          <t>TARGET_UPDATE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1916,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,7 +1972,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Expression</t>
+          <t>Source Qualifier</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1957,7 +1980,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IIF logic for contract charges, UPPER transformation</t>
+          <t>SQ_Churndata, SQ_Gender</t>
         </is>
       </c>
     </row>
@@ -1969,15 +1992,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joiner</t>
+          <t>Expression</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Join churn data with gender lookup</t>
+          <t>EXPTRANS, EXPTRANS1</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2012,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sorter</t>
+          <t>Joiner</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1997,7 +2020,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sort by gender, SeniorCitizen, Partner</t>
+          <t>JNRTRANS1</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aggregator</t>
+          <t>Sorter</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2017,27 +2040,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Group by gender, Contract, calculate totals</t>
+          <t>SRTTRANS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wf_s_m_multiple_unc11</t>
+          <t>wf_m_PatternForChurnData</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unconnected Lookup</t>
+          <t>Aggregator</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DDEPT and EMP_LOC lookups converted to broadcast joins</t>
+          <t>AGGTRANS</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2072,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Source Qualifier</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2057,7 +2080,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Filter based on lookup result</t>
+          <t>SQ_EMPLOYEE</t>
         </is>
       </c>
     </row>
@@ -2069,27 +2092,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aggregator</t>
+          <t>Lookup (Unconnected)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAX/MIN salary calculations</t>
+          <t>LKPTRANS, LKPTRANS1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wf_s_m_multiple_mapplet</t>
+          <t>wf_s_m_multiple_unc11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mapplet</t>
+          <t>Expression</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2097,19 +2120,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>mp_emp and mp_lkp_loc inlined</t>
+          <t>EXPTRANS, EXPTRANS1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wf_s_m_multiple_mapplet</t>
+          <t>wf_s_m_multiple_unc11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Expression</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2117,19 +2140,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Concatenate FIRSTNAME and LASTNAME</t>
+          <t>FILTRANS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wf_m_mapplet_multiple_unconnected</t>
+          <t>wf_s_m_multiple_unc11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mapplet</t>
+          <t>Aggregator</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2137,79 +2160,79 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mp_mutiple_unc with unconnected lookups</t>
+          <t>AGGTRANS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wf_m_mapplet_multiple_unconnected</t>
+          <t>wf_s_m_multiple_mapplet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unconnected Lookup</t>
+          <t>Source Qualifier</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DEPTNO-&gt;DNAME and DEPTNO-&gt;LOC lookups</t>
+          <t>SQ_EMPLOYEEDETAILS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wf_s_m_complex5</t>
+          <t>wf_s_m_multiple_mapplet</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Mapplet</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Combine 4 employee sources</t>
+          <t>mp_emp, mp_lkp_loc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wf_s_m_complex5</t>
+          <t>wf_s_m_multiple_mapplet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Expression</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Route by DEPID (10 vs DEFAULT)</t>
+          <t>EXPTRANS_1, COM_EXPTRANS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wf_s_m_complex5</t>
+          <t>wf_m_mapplet_multiple_unconnected</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Joiner</t>
+          <t>Source Qualifier</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2217,19 +2240,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Join employee with department</t>
+          <t>SQ_EMPLOYEE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wf_s_m_complex5</t>
+          <t>wf_m_mapplet_multiple_unconnected</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aggregator</t>
+          <t>Mapplet</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2237,27 +2260,247 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MAX/MIN salary by department</t>
+          <t>mp_mutiple_unc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wf_s_m_complex5</t>
+          <t>wf_m_mapplet_multiple_unconnected</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EXPTRANS, EXPTRANS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Source Qualifier</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Multiple source qualifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>UNTRANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sorter</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SRTTRANS, SRTTRANS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Joiner</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>JNRTRANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mapplet</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mp_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Expression</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EXPTRANS, EXPTRANS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Aggregator</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AGGTRANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Router</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RTRTRANS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LKPTRANS, LKPTRANS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FILTRANS_INSERT, FILTRANS_UPDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>wf_s_m_complex5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Update Strategy</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Flag-based insert/update logic</t>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UPDTRANS</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,12 +2541,14 @@
           <t>Total Jobs Migrated</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>5</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2558,14 @@
           <t>Total Source Tables</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>12</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2575,14 @@
           <t>Total Target Tables</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>12</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
@@ -2343,87 +2592,65 @@
           <t>Total Transformations</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>18</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Converted</t>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unconnected Lookups</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6</v>
+          <t>Jobs with Exact Row Match</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Converted to Broadcast Joins</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Router Transformations</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
+          <t>Jobs with Expected Differences</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Converted to Filter Branches</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Union Transformations</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
+          <t>Migration Validation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Converted to union()</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mapplets</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Inlined</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Validation Status</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>All PASS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
